--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,228 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120288360</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Idre, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>382943</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6860035</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120288359</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Idre, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>383061</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6859783</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>120288360</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>120288359</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288360</v>
+        <v>120288359</v>
       </c>
       <c r="B4" t="n">
         <v>91858</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382943</v>
+        <v>383061</v>
       </c>
       <c r="R4" t="n">
-        <v>6860035</v>
+        <v>6859783</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288359</v>
+        <v>120288360</v>
       </c>
       <c r="B5" t="n">
         <v>91858</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>383061</v>
+        <v>382943</v>
       </c>
       <c r="R5" t="n">
-        <v>6859783</v>
+        <v>6860035</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288359</v>
+        <v>120288360</v>
       </c>
       <c r="B4" t="n">
         <v>91858</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>383061</v>
+        <v>382943</v>
       </c>
       <c r="R4" t="n">
-        <v>6859783</v>
+        <v>6860035</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288360</v>
+        <v>120288359</v>
       </c>
       <c r="B5" t="n">
         <v>91858</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>382943</v>
+        <v>383061</v>
       </c>
       <c r="R5" t="n">
-        <v>6860035</v>
+        <v>6859783</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97909514</v>
+        <v>120288360</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
+        <v>91908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382943.1394994155</v>
+        <v>382943</v>
       </c>
       <c r="R2" t="n">
-        <v>6860035.371703668</v>
+        <v>6860035</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +752,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1026,117 +1016,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>120288360</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91908</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Idre, Dlr</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>382943</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6860035</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44407-2021 artfynd.xlsx
+++ b/artfynd/A 44407-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288359</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288360</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>